--- a/양식/견적서양식_비조명.xlsx
+++ b/양식/견적서양식_비조명.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fivep\OneDrive\Desktop\CLAUDEestimate\auto_make\양식\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8592"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22785" windowHeight="8595"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -178,7 +183,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -730,7 +735,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -767,9 +772,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -826,15 +828,6 @@
     </xf>
     <xf numFmtId="41" fontId="6" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1"/>
@@ -854,15 +847,96 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -876,6 +950,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -902,89 +988,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="2" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1228,7 +1236,7 @@
         <xdr:cNvPr id="2" name="그림 1" descr="도장.tif">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1305,7 +1313,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1340,7 +1348,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1551,65 +1559,65 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="17.69921875" customWidth="1"/>
-    <col min="2" max="2" width="8.19921875" customWidth="1"/>
+    <col min="1" max="1" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="8.25" customWidth="1"/>
     <col min="3" max="3" width="7.5" customWidth="1"/>
     <col min="4" max="4" width="5.5" customWidth="1"/>
-    <col min="5" max="5" width="0.8984375" customWidth="1"/>
+    <col min="5" max="5" width="0.875" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
-    <col min="7" max="7" width="10.8984375" customWidth="1"/>
-    <col min="8" max="8" width="7.09765625" customWidth="1"/>
+    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="8" max="8" width="7.125" customWidth="1"/>
     <col min="9" max="9" width="10.5" customWidth="1"/>
-    <col min="12" max="12" width="9.59765625" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="38.4">
-      <c r="A1" s="63" t="s">
+    <row r="1" spans="1:9" ht="38.25">
+      <c r="A1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="65"/>
-    </row>
-    <row r="2" spans="1:9" ht="18" thickBot="1">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="37"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="59"/>
+    </row>
+    <row r="2" spans="1:9" ht="17.25" thickBot="1">
+      <c r="A2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="53" t="s">
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="54"/>
-      <c r="F3" s="24" t="s">
+      <c r="E3" s="81"/>
+      <c r="F3" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="66" t="s">
+      <c r="G3" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="67"/>
-    </row>
-    <row r="4" spans="1:9" ht="27" thickBot="1">
-      <c r="A4" s="39" t="s">
+      <c r="H3" s="60"/>
+      <c r="I3" s="61"/>
+    </row>
+    <row r="4" spans="1:9" ht="24.75" thickBot="1">
+      <c r="A4" s="35" t="s">
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1618,9 +1626,9 @@
       <c r="C4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="25" t="s">
+      <c r="D4" s="82"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="24" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -1629,127 +1637,127 @@
       <c r="H4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="27" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="40"/>
+      <c r="A5" s="36"/>
       <c r="B5" s="5"/>
       <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="55"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="25" t="s">
+      <c r="D5" s="82"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="68"/>
-      <c r="I5" s="69"/>
-    </row>
-    <row r="6" spans="1:9" ht="18" thickBot="1">
-      <c r="A6" s="70" t="s">
+      <c r="H5" s="62"/>
+      <c r="I5" s="63"/>
+    </row>
+    <row r="6" spans="1:9" ht="17.25" thickBot="1">
+      <c r="A6" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="71"/>
+      <c r="B6" s="65"/>
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="55"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="25" t="s">
+      <c r="D6" s="82"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="72" t="s">
+      <c r="G6" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="72"/>
-      <c r="I6" s="73"/>
-    </row>
-    <row r="7" spans="1:9" ht="18" thickBot="1">
-      <c r="A7" s="76"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="26" t="s">
+      <c r="H6" s="66"/>
+      <c r="I6" s="67"/>
+    </row>
+    <row r="7" spans="1:9" ht="17.25" thickBot="1">
+      <c r="A7" s="46"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="79"/>
-      <c r="I7" s="80"/>
-    </row>
-    <row r="8" spans="1:9" ht="18" thickBot="1">
-      <c r="A8" s="35"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="50"/>
+    </row>
+    <row r="8" spans="1:9" ht="17.25" thickBot="1">
+      <c r="A8" s="31"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="41"/>
+      <c r="I8" s="37"/>
     </row>
     <row r="9" spans="1:9" ht="23.1" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="82"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="52"/>
     </row>
     <row r="10" spans="1:9" ht="23.1" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="83">
+      <c r="B10" s="53">
         <f>G30</f>
         <v>290000</v>
       </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="85">
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="55">
         <f>B10</f>
         <v>290000</v>
       </c>
-      <c r="I10" s="86"/>
+      <c r="I10" s="56"/>
     </row>
     <row r="11" spans="1:9" ht="23.1" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="74"/>
-      <c r="F11" s="33" t="s">
+      <c r="E11" s="44"/>
+      <c r="F11" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="75" t="s">
+      <c r="G11" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="75"/>
+      <c r="H11" s="45"/>
       <c r="I11" s="10" t="s">
         <v>20</v>
       </c>
@@ -1758,263 +1766,248 @@
       <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="13">
+      <c r="B12" s="40"/>
+      <c r="C12" s="12">
         <v>1</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="48"/>
-      <c r="F12" s="14">
+      <c r="E12" s="71"/>
+      <c r="F12" s="13">
         <v>40000</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="72">
         <v>40000</v>
       </c>
-      <c r="H12" s="50"/>
-      <c r="I12" s="15"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="13">
+      <c r="B13" s="40"/>
+      <c r="C13" s="12">
         <v>1</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="14">
+      <c r="E13" s="68"/>
+      <c r="F13" s="13">
         <v>250000</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="69">
         <v>250000</v>
       </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="15"/>
-    </row>
-    <row r="14" spans="1:9" ht="22.8" customHeight="1">
-      <c r="A14" s="42"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="15"/>
-    </row>
-    <row r="15" spans="1:9" ht="22.8" customHeight="1">
-      <c r="A15" s="42"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="15"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="14"/>
+    </row>
+    <row r="14" spans="1:9" ht="22.9" customHeight="1">
+      <c r="A14" s="86"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="1:9" ht="22.9" customHeight="1">
+      <c r="A15" s="86"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="14"/>
     </row>
     <row r="16" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A16" s="43"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="15"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="14"/>
     </row>
     <row r="17" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A17" s="43"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="15"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="14"/>
     </row>
     <row r="18" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A18" s="44"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="15"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="14"/>
     </row>
     <row r="19" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A19" s="43"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="15"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="14"/>
     </row>
     <row r="20" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A20" s="43"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="15"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="14"/>
     </row>
     <row r="21" spans="1:9" ht="23.1" customHeight="1">
       <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="18"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" spans="1:9" ht="23.1" customHeight="1">
       <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="18"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="17"/>
     </row>
     <row r="23" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A23" s="19"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="18"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="24" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A24" s="19"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="18"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="17"/>
     </row>
     <row r="25" spans="1:9" ht="23.1" customHeight="1">
       <c r="A25" s="11"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="18"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" spans="1:9" ht="23.1" customHeight="1">
       <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="18"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="17"/>
     </row>
     <row r="27" spans="1:9" ht="23.1" customHeight="1">
       <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="18"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="17"/>
     </row>
     <row r="28" spans="1:9" ht="23.1" customHeight="1">
       <c r="A28" s="11"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="18"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" spans="1:9" ht="23.1" customHeight="1">
-      <c r="A29" s="19"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="18"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" spans="1:9" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A30" s="20"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="52">
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="79">
         <f>SUM(G12:H23)</f>
         <v>290000</v>
       </c>
-      <c r="H30" s="52"/>
-      <c r="I30" s="23" t="s">
+      <c r="H30" s="79"/>
+      <c r="I30" s="22" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="D30:E30"/>
@@ -2031,16 +2024,31 @@
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="H10:I10"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -2053,7 +2061,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -2065,7 +2073,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5"/>
   <sheetData/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
